--- a/exit_interview_templates/008_network_exit_feedback_survey--exit_interview_templates.xlsx
+++ b/exit_interview_templates/008_network_exit_feedback_survey--exit_interview_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1_-_very_dissatisfied'}</t>
+          <t>1_-_very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1 - Very Dissatisfied'}</t>
+          <t>1 - Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2_-_somewhat_dissatisfied'}</t>
+          <t>2_-_somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2 - Somewhat Dissatisfied'}</t>
+          <t>2 - Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4_-_somewhat_satisfied'}</t>
+          <t>4_-_somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4 - Somewhat Satisfied'}</t>
+          <t>4 - Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5_-_very_satisfied'}</t>
+          <t>5_-_very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5 - Very Satisfied'}</t>
+          <t>5 - Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'almost_daily'}</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Almost Daily'}</t>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1_-_very_low'}</t>
+          <t>1_-_very_low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1 - Very Low'}</t>
+          <t>1 - Very Low</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2_-_low'}</t>
+          <t>2_-_low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2 - Low'}</t>
+          <t>2 - Low</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4_-_high'}</t>
+          <t>4_-_high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4 - High'}</t>
+          <t>4 - High</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5_-_very_high'}</t>
+          <t>5_-_very_high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5 - Very High'}</t>
+          <t>5 - Very High</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1_-_very_poor'}</t>
+          <t>1_-_very_poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1 - Very Poor'}</t>
+          <t>1 - Very Poor</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2_-_poor'}</t>
+          <t>2_-_poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2 - Poor'}</t>
+          <t>2 - Poor</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3_-_neutral'}</t>
+          <t>3_-_neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3 - Neutral'}</t>
+          <t>3 - Neutral</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4_-_good'}</t>
+          <t>4_-_good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4 - Good'}</t>
+          <t>4 - Good</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5_-_excellent'}</t>
+          <t>5_-_excellent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5 - Excellent'}</t>
+          <t>5 - Excellent</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'2-3_hours'}</t>
+          <t>2-3_hours</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '2-3 hours'}</t>
+          <t>2-3 hours</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_3_hours'}</t>
+          <t>more_than_3_hours</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than 3 hours'}</t>
+          <t>More than 3 hours</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
